--- a/site/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,688 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Key Functions</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>h_01M07HMQ0ZQV4QQDNK58D8E31C</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07HMQ0ZQV4QQDNK58D8E31C</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>h_01M07HSM87J5NM40XX56WFYJVJ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07HSM87J5NM40XX56WFYJVJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Integration Setup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01M07HWJJ79W5Y89SHBR212A4M</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07HWJJ79W5Y89SHBR212A4M</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Create Integration</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01M07HYZAP74FABFVASG3127DJ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07HYZAP74FABFVASG3127DJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01M07J094ZQWQY9G7Q0DQFG0B7</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07J094ZQWQY9G7Q0DQFG0B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01M07JAQTQ44DKYMXC246ZQ2BV</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07JAQTQ44DKYMXC246ZQ2BV</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Application Settings</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01M07JXNX5B9F7YRRE166PMAV8</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07JXNX5B9F7YRRE166PMAV8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Filter Employees</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01M07K878W8V33JPJ91JH82X2F</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07K878W8V33JPJ91JH82X2F</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Employee Filter Configuration</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01M07KG8CSW5NB8M1GYQR1ZA2H</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07KG8CSW5NB8M1GYQR1ZA2H</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Service Desk</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01M07KR1XRH7MB5MGKEGM0MJZF</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07KR1XRH7MB5MGKEGM0MJZF</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01M07KY9X7G87CR498RQ7G8JYR</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07KY9X7G87CR498RQ7G8JYR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Service Desk Application Configuration</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01M07M20N6HHPE35WNNFXRVYV2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07M20N6HHPE35WNNFXRVYV2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Messaging Application</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01M07M5H23BC8B8DWMJ6Q01ZDR</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07M5H23BC8B8DWMJ6Q01ZDR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>JML Ticket Creation</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01M07M6G8AP6TYC486236DJAW2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07M6G8AP6TYC486236DJAW2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ticket Creation Configuration</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01M07M95Z6VCJ92JM1XTDRFQDP</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07M95Z6VCJ92JM1XTDRFQDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01M07R487BNTVDS47PD9D9ZFJX</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07R487BNTVDS47PD9D9ZFJX</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01M07R9KYR8V4RDCCEXJDVCS1X</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07R9KYR8V4RDCCEXJDVCS1X</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Define Notification Channel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Notification Configuration</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Global Operational Settings</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01M07REJ4XZVJW4SJVXEKF4KFP</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07REJ4XZVJW4SJVXEKF4KFP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Logging Settings</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01KV86ERRYGWDMSKMK5YKZMPR9</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Log Insight Settings</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KV86ERRYCD184XX20ETKPWPR</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01KV86ERRYCD184XX20ETKPWPR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01M07RFYENETD0EQRPG939A00W</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07RFYENETD0EQRPG939A00W</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Advanced Settings</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01KS28NHEHVRN9BPPCKGXGAYYN</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Features</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01M07RY94WBQJAVVE9VY4VZ43J</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07RY94WBQJAVVE9VY4VZ43J</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Service Desk Bridge</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KW1TH82EGE4EW275DJSB2X28</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01KW1TH82EGE4EW275DJSB2X28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01M07S5JXHY2CJF742CR5CRVZ5</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07S5JXHY2CJF742CR5CRVZ5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,73 +1013,73 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Features</t>
+          <t>Operating Safeguard Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01M07RY94WBQJAVVE9VY4VZ43J</t>
+          <t>h_01M1K9ZGWYQVHQY8WCP8THHR3N</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07RY94WBQJAVVE9VY4VZ43J</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M1K9ZGWYQVHQY8WCP8THHR3N</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Service Desk Bridge</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KW1TH82EGE4EW275DJSB2X28</t>
+          <t>h_01M07RY94WBQJAVVE9VY4VZ43J</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01KW1TH82EGE4EW275DJSB2X28</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07RY94WBQJAVVE9VY4VZ43J</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Service Desk Bridge</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01M07S5JXHY2CJF742CR5CRVZ5</t>
+          <t>h_01KW1TH82EGE4EW275DJSB2X28</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07S5JXHY2CJF742CR5CRVZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01KW1TH82EGE4EW275DJSB2X28</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,54 +1089,76 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>h_01M07S5JXHY2CJF742CR5CRVZ5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01M07S5JXHY2CJF742CR5CRVZ5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Manage-Engine-Service-Desk-Plus-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
